--- a/data/trans_orig/Q5416-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5416-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse por su casa en 2007</t>
+          <t>Población según si es capaz de moverse por su casa en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>830</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7816</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16095</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19340</t>
+          <t>19942</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16861</t>
+          <t>16472</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30841</t>
+          <t>30710</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +896,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>29586</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>19640</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>41237</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>2,04%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>29586</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>20327</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>42122</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11836</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13217</t>
+          <t>14332</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>352018</t>
+          <t>351904</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>365639</t>
+          <t>365649</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>541020</t>
+          <t>540192</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>564712</t>
+          <t>563148</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>899681</t>
+          <t>899740</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>926416</t>
+          <t>926011</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -1302,97 +1302,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1875</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5762</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>5663</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>6655</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>6801</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1528,97 +1528,97 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1875</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1922</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83994</t>
+          <t>83871</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55108</t>
+          <t>54942</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>141928</t>
+          <t>141898</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>149496</t>
+          <t>149471</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -1871,97 +1871,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1984,97 +1984,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2097,97 +2097,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1274</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5930</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>22,06%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1274</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6412</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>7520</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>23,85%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>7583</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41194</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20469</t>
+          <t>20951</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60492</t>
+          <t>60555</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>830</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>21080</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18399</t>
+          <t>18310</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13094</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32095</t>
+          <t>32747</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21128</t>
+          <t>21768</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44083</t>
+          <t>43671</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13380</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14438</t>
+          <t>14575</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>478730</t>
+          <t>480822</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>493920</t>
+          <t>494332</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>626662</t>
+          <t>625528</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>651232</t>
+          <t>649966</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1113874</t>
+          <t>1112749</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1141281</t>
+          <t>1140217</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse por su casa en 2012</t>
+          <t>Población según si es capaz de moverse por su casa en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16865</t>
+          <t>17928</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>15780</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35891</t>
+          <t>36200</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21270</t>
+          <t>22487</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44874</t>
+          <t>45901</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17037</t>
+          <t>18121</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22558</t>
+          <t>21894</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44906</t>
+          <t>45993</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30549</t>
+          <t>30424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57366</t>
+          <t>55621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13650</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16246</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>380290</t>
+          <t>380581</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399597</t>
+          <t>400840</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>558938</t>
+          <t>558375</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>588406</t>
+          <t>589548</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>947801</t>
+          <t>946957</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>983917</t>
+          <t>983101</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -3809,97 +3809,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2424</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2146</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>8026</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>9,66%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>2424</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>8340</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>7690</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>10,04%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>2424</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>7635</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -4035,97 +4035,97 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2146</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>2115</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>112263</t>
+          <t>111358</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>73463</t>
+          <t>73729</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82017</t>
+          <t>82056</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>189569</t>
+          <t>189789</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>199668</t>
+          <t>199625</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -4378,97 +4378,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2222</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2331</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4491,97 +4491,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4560</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>20,5%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>1053</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>5210</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>5898</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>23,42%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1053</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>5486</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20352</t>
+          <t>21883</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15788</t>
+          <t>15289</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41280</t>
+          <t>40809</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47864</t>
+          <t>47851</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17012</t>
+          <t>16695</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17058</t>
+          <t>17124</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37752</t>
+          <t>37547</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24421</t>
+          <t>24160</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49355</t>
+          <t>49277</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20320</t>
+          <t>19239</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23993</t>
+          <t>24292</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47287</t>
+          <t>47828</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33099</t>
+          <t>33060</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>59940</t>
+          <t>61184</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>972</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12508</t>
+          <t>13003</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11053</t>
+          <t>10237</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>18924</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>522543</t>
+          <t>523398</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>542765</t>
+          <t>543478</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>657558</t>
+          <t>657186</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>688842</t>
+          <t>689517</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1188806</t>
+          <t>1190030</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1227759</t>
+          <t>1228066</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse por su casa en 2016</t>
+          <t>Población según si es capaz de moverse por su casa en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>907</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23131</t>
+          <t>23730</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9525</t>
+          <t>9444</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27892</t>
+          <t>28948</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23196</t>
+          <t>23173</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24732</t>
+          <t>25952</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50810</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69407</t>
+          <t>67401</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8730</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>323263</t>
+          <t>323378</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>340626</t>
+          <t>340232</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>488610</t>
+          <t>486708</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>517360</t>
+          <t>516819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>818402</t>
+          <t>818052</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>853282</t>
+          <t>852195</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,62 +6351,62 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2283</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>6418</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1804</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>5978</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12381</t>
+          <t>12375</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>2364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15293</t>
+          <t>13476</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>183939</t>
+          <t>183341</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>174353</t>
+          <t>174263</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185580</t>
+          <t>185604</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>360939</t>
+          <t>361782</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374949</t>
+          <t>375368</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -6885,97 +6885,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -7111,97 +7111,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34386</t>
+          <t>35833</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65936</t>
+          <t>66518</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11678</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22743</t>
+          <t>23794</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10539</t>
+          <t>11123</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29584</t>
+          <t>30766</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26518</t>
+          <t>25886</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31208</t>
+          <t>31679</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59464</t>
+          <t>60155</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47523</t>
+          <t>46009</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>79617</t>
+          <t>78811</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>841</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8282</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9146</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>12235</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>552307</t>
+          <t>552318</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>570710</t>
+          <t>571503</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>698456</t>
+          <t>699425</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>731173</t>
+          <t>732410</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1258359</t>
+          <t>1257711</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1296262</t>
+          <t>1296530</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse por su casa en 2023</t>
+          <t>Población según si es capaz de moverse por su casa en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>7774</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>8637</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20025</t>
+          <t>19184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11735</t>
+          <t>11897</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23679</t>
+          <t>24454</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11889</t>
+          <t>11820</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29177</t>
+          <t>29135</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47392</t>
+          <t>47145</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33815</t>
+          <t>34624</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53058</t>
+          <t>53190</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -8485,7 +8485,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12728</t>
+          <t>13293</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14361</t>
+          <t>14984</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>251624</t>
+          <t>251414</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>262090</t>
+          <t>262016</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>430723</t>
+          <t>431204</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>451908</t>
+          <t>453706</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>688669</t>
+          <t>686265</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>712694</t>
+          <t>711197</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,37%</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>750</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>7376</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9568</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16429</t>
+          <t>15863</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20072</t>
+          <t>20432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>519</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>260231</t>
+          <t>260004</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>269438</t>
+          <t>269057</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>432954</t>
+          <t>434292</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>452249</t>
+          <t>452436</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>701085</t>
+          <t>700404</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>721314</t>
+          <t>720489</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -9392,97 +9392,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9505,97 +9505,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2134</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>381</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>1917</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1915</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>816</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9653,62 +9653,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>856</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -9731,7 +9731,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104169</t>
+          <t>104170</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69408</t>
+          <t>69191</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>174074</t>
+          <t>174167</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2314</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9530</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>7470</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22367</t>
+          <t>22888</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>13064</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28040</t>
+          <t>27795</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>6937</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17836</t>
+          <t>17861</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22532</t>
+          <t>20028</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59994</t>
+          <t>60436</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36747</t>
+          <t>35904</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>70118</t>
+          <t>69848</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>820</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15537</t>
+          <t>15291</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18657</t>
+          <t>18428</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>620506</t>
+          <t>620574</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>634459</t>
+          <t>634588</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>936851</t>
+          <t>936664</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>990609</t>
+          <t>995233</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1568778</t>
+          <t>1567766</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1618743</t>
+          <t>1616412</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5416-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5416-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>822</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>16472</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>19726</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16472</t>
+          <t>17086</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12524</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30710</t>
+          <t>31242</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19640</t>
+          <t>19535</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41237</t>
+          <t>42566</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>11796</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14332</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>351904</t>
+          <t>351786</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>365649</t>
+          <t>365751</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>540192</t>
+          <t>541271</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>563148</t>
+          <t>564369</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>899740</t>
+          <t>897769</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>926011</t>
+          <t>925552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,77 +1435,77 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5266</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>7187</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>4,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4578</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1723</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5650</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83871</t>
+          <t>83918</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54942</t>
+          <t>55259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>141898</t>
+          <t>141236</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>149471</t>
+          <t>149481</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>21695</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60555</t>
+          <t>61280</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>831</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>16618</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21080</t>
+          <t>21256</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18310</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13635</t>
+          <t>13389</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32747</t>
+          <t>32500</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21768</t>
+          <t>21365</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43671</t>
+          <t>43343</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14575</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>480822</t>
+          <t>480006</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>494332</t>
+          <t>494104</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>625528</t>
+          <t>626168</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>649966</t>
+          <t>649874</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1112749</t>
+          <t>1113102</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1140217</t>
+          <t>1140342</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>17025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15780</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36200</t>
+          <t>36537</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22487</t>
+          <t>22689</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45901</t>
+          <t>47006</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18121</t>
+          <t>17227</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21894</t>
+          <t>22234</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45993</t>
+          <t>44149</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30424</t>
+          <t>30040</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55621</t>
+          <t>55738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13528</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16105</t>
+          <t>15591</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>380581</t>
+          <t>381117</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>400840</t>
+          <t>400420</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>558375</t>
+          <t>558497</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>589548</t>
+          <t>589215</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>946957</t>
+          <t>948231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>983101</t>
+          <t>983925</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7690</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>979</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>9276</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111358</t>
+          <t>111281</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>73729</t>
+          <t>73244</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82056</t>
+          <t>82037</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>189789</t>
+          <t>189029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>199625</t>
+          <t>199611</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21883</t>
+          <t>22119</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15289</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40809</t>
+          <t>40213</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47851</t>
+          <t>47900</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16783</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17124</t>
+          <t>16951</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37547</t>
+          <t>37687</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24160</t>
+          <t>25460</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49277</t>
+          <t>49608</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19239</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24292</t>
+          <t>23799</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47828</t>
+          <t>46194</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33060</t>
+          <t>34340</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61184</t>
+          <t>61636</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>12403</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>11136</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18924</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>523398</t>
+          <t>521963</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>543478</t>
+          <t>543602</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>657186</t>
+          <t>657871</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>689517</t>
+          <t>689205</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1190030</t>
+          <t>1190186</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1228066</t>
+          <t>1227313</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>913</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23730</t>
+          <t>23052</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>9648</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28948</t>
+          <t>27301</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23173</t>
+          <t>23014</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25952</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>51496</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38955</t>
+          <t>37965</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67401</t>
+          <t>67514</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>764</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>958</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>323378</t>
+          <t>324499</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>340232</t>
+          <t>340481</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>486708</t>
+          <t>486229</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>516819</t>
+          <t>517365</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>818052</t>
+          <t>817429</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>852195</t>
+          <t>851976</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,76%</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>5165</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12375</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>183341</t>
+          <t>183867</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>191614</t>
+          <t>191540</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>174263</t>
+          <t>173708</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185604</t>
+          <t>185443</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>361782</t>
+          <t>360766</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375368</t>
+          <t>374608</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9185</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35833</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66518</t>
+          <t>65844</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10992</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6359</t>
+          <t>6216</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23794</t>
+          <t>23604</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,47 +7504,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>18534</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>11190</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>30546</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>18534</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>11123</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>30766</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25886</t>
+          <t>24787</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31679</t>
+          <t>31660</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60155</t>
+          <t>61237</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46009</t>
+          <t>45159</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78811</t>
+          <t>79278</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>886</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6997</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12235</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>552318</t>
+          <t>552919</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>571503</t>
+          <t>570833</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>699425</t>
+          <t>697398</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>732410</t>
+          <t>731603</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1257711</t>
+          <t>1259202</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1296530</t>
+          <t>1297880</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -8249,22 +8249,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7774</t>
+          <t>8791</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13361</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19184</t>
+          <t>20920</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>18348</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11897</t>
+          <t>12932</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24454</t>
+          <t>25733</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11820</t>
+          <t>12391</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37046</t>
+          <t>40252</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29135</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47145</t>
+          <t>50295</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>43354</t>
+          <t>47174</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34624</t>
+          <t>38101</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53190</t>
+          <t>59480</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>5617</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>8787</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13293</t>
+          <t>14542</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14984</t>
+          <t>16255</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>257942</t>
+          <t>277666</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>251414</t>
+          <t>270768</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>262016</t>
+          <t>282797</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>442547</t>
+          <t>475429</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>431204</t>
+          <t>463738</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>453706</t>
+          <t>487098</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>700489</t>
+          <t>753095</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>686265</t>
+          <t>739505</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>711197</t>
+          <t>764544</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,24%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>769976</t>
+          <t>828876</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>769976</t>
+          <t>828876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>769976</t>
+          <t>828876</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -8828,12 +8828,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15863</t>
+          <t>13860</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12200</t>
+          <t>13673</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20432</t>
+          <t>20967</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -9044,7 +9044,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -9054,12 +9054,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>598</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>265837</t>
+          <t>296038</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>260004</t>
+          <t>289992</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>269057</t>
+          <t>299662</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>445084</t>
+          <t>265266</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>434292</t>
+          <t>259253</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>452436</t>
+          <t>269359</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>710921</t>
+          <t>561304</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>700404</t>
+          <t>553465</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>720489</t>
+          <t>567824</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>397</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -9545,12 +9545,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>397</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -9580,12 +9580,12 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>659</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -9623,12 +9623,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>659</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -9693,12 +9693,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -9726,27 +9726,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>104828</t>
+          <t>118222</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104170</t>
+          <t>114899</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -9761,27 +9761,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>70944</t>
+          <t>82458</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69191</t>
+          <t>80694</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -9796,27 +9796,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>175772</t>
+          <t>200681</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>174167</t>
+          <t>197988</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2427</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15280</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22888</t>
+          <t>23766</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>20335</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13064</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27795</t>
+          <t>29637</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11126</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17861</t>
+          <t>18843</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>44809</t>
+          <t>49139</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20028</t>
+          <t>38962</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60436</t>
+          <t>60166</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>55935</t>
+          <t>61243</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35904</t>
+          <t>49744</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69848</t>
+          <t>74787</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>7680</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>10692</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15291</t>
+          <t>16951</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>8621</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18428</t>
+          <t>20795</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>628607</t>
+          <t>691926</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>620574</t>
+          <t>683654</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>634588</t>
+          <t>698477</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>958575</t>
+          <t>823153</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>936664</t>
+          <t>809401</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>995233</t>
+          <t>834765</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1587181</t>
+          <t>1515080</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1567766</t>
+          <t>1498880</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1616412</t>
+          <t>1530536</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1027797</t>
+          <t>899282</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1027797</t>
+          <t>899282</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1027797</t>
+          <t>899282</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1675283</t>
+          <t>1612083</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1675283</t>
+          <t>1612083</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1675283</t>
+          <t>1612083</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
